--- a/outputs/candidates/baseline/candidate_05_expert_style.xlsx
+++ b/outputs/candidates/baseline/candidate_05_expert_style.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="261">
   <si>
     <t>candidate_id</t>
   </si>
@@ -541,15 +541,12 @@
     <t>DRV_027</t>
   </si>
   <si>
-    <t>DRV_018</t>
+    <t>DRV_022</t>
   </si>
   <si>
     <t>DRV_020</t>
   </si>
   <si>
-    <t>DRV_022</t>
-  </si>
-  <si>
     <t>DRV_005</t>
   </si>
   <si>
@@ -589,13 +586,10 @@
     <t>이섭민</t>
   </si>
   <si>
-    <t>박영준</t>
+    <t>오준원</t>
   </si>
   <si>
     <t>김진무</t>
-  </si>
-  <si>
-    <t>오준원</t>
   </si>
   <si>
     <t>문하인</t>
@@ -1323,7 +1317,7 @@
         <v>169</v>
       </c>
       <c r="V2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="W2">
         <v>78</v>
@@ -1338,7 +1332,7 @@
         <v>1</v>
       </c>
       <c r="AD2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:30">
@@ -1403,7 +1397,7 @@
         <v>154</v>
       </c>
       <c r="V3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="W3">
         <v>70</v>
@@ -1418,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:30">
@@ -1483,7 +1477,7 @@
         <v>155</v>
       </c>
       <c r="V4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="W4">
         <v>70</v>
@@ -1498,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="AD4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:30">
@@ -1563,7 +1557,7 @@
         <v>156</v>
       </c>
       <c r="V5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="W5">
         <v>70</v>
@@ -1578,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="AD5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:30">
@@ -1643,7 +1637,7 @@
         <v>156</v>
       </c>
       <c r="V6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="W6">
         <v>70</v>
@@ -1658,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="AD6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:30">
@@ -1723,7 +1717,7 @@
         <v>157</v>
       </c>
       <c r="V7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="W7">
         <v>70</v>
@@ -1738,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="AD7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:30">
@@ -1806,7 +1800,7 @@
         <v>170</v>
       </c>
       <c r="V8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W8">
         <v>70</v>
@@ -1821,7 +1815,7 @@
         <v>1</v>
       </c>
       <c r="AD8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:30">
@@ -1889,7 +1883,7 @@
         <v>171</v>
       </c>
       <c r="V9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="W9">
         <v>70</v>
@@ -1904,7 +1898,7 @@
         <v>1</v>
       </c>
       <c r="AD9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:30">
@@ -1972,7 +1966,7 @@
         <v>172</v>
       </c>
       <c r="V10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="W10">
         <v>70</v>
@@ -1987,7 +1981,7 @@
         <v>1</v>
       </c>
       <c r="AD10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:30">
@@ -2055,7 +2049,7 @@
         <v>173</v>
       </c>
       <c r="V11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="W11">
         <v>70</v>
@@ -2070,7 +2064,7 @@
         <v>1</v>
       </c>
       <c r="AD11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:30">
@@ -2138,7 +2132,7 @@
         <v>174</v>
       </c>
       <c r="V12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="W12">
         <v>70</v>
@@ -2153,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="AD12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:30">
@@ -2221,7 +2215,7 @@
         <v>175</v>
       </c>
       <c r="V13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="W13">
         <v>70</v>
@@ -2236,7 +2230,7 @@
         <v>1</v>
       </c>
       <c r="AD13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:30">
@@ -2301,10 +2295,10 @@
         <v>161</v>
       </c>
       <c r="U14" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="V14" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="W14">
         <v>70</v>
@@ -2319,7 +2313,7 @@
         <v>1</v>
       </c>
       <c r="AD14" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:30">
@@ -2384,10 +2378,10 @@
         <v>162</v>
       </c>
       <c r="U15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="V15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="W15">
         <v>70</v>
@@ -2402,7 +2396,7 @@
         <v>1</v>
       </c>
       <c r="AD15" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" spans="1:30">
@@ -2467,10 +2461,10 @@
         <v>163</v>
       </c>
       <c r="U16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="V16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="W16">
         <v>70</v>
@@ -2485,7 +2479,7 @@
         <v>1</v>
       </c>
       <c r="AD16" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" spans="1:30">
@@ -2550,10 +2544,10 @@
         <v>164</v>
       </c>
       <c r="U17" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="V17" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="W17">
         <v>70</v>
@@ -2568,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="AD17" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:30">
@@ -2633,10 +2627,10 @@
         <v>164</v>
       </c>
       <c r="U18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="V18" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="W18">
         <v>70</v>
@@ -2651,7 +2645,7 @@
         <v>1</v>
       </c>
       <c r="AD18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" spans="1:30">
@@ -2716,10 +2710,10 @@
         <v>165</v>
       </c>
       <c r="U19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="V19" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="W19">
         <v>70</v>
@@ -2734,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="AD19" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:30">
@@ -2799,10 +2793,10 @@
         <v>165</v>
       </c>
       <c r="U20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="V20" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="W20">
         <v>70</v>
@@ -2817,7 +2811,7 @@
         <v>0</v>
       </c>
       <c r="AD20" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21" spans="1:30">
@@ -2882,10 +2876,10 @@
         <v>165</v>
       </c>
       <c r="U21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="V21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="W21">
         <v>70</v>
@@ -2900,7 +2894,7 @@
         <v>0</v>
       </c>
       <c r="AD21" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22" spans="1:30">
@@ -2965,10 +2959,10 @@
         <v>166</v>
       </c>
       <c r="U22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="V22" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="W22">
         <v>75</v>
@@ -2983,7 +2977,7 @@
         <v>1</v>
       </c>
       <c r="AD22" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23" spans="1:30">
@@ -3048,10 +3042,10 @@
         <v>167</v>
       </c>
       <c r="U23" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="W23">
         <v>70</v>
@@ -3066,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="AD23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24" spans="1:30">
@@ -3131,10 +3125,10 @@
         <v>168</v>
       </c>
       <c r="U24" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="V24" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="W24">
         <v>75</v>
@@ -3149,7 +3143,7 @@
         <v>1</v>
       </c>
       <c r="AD24" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" spans="1:30">
@@ -3214,10 +3208,10 @@
         <v>168</v>
       </c>
       <c r="U25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V25" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="W25">
         <v>75</v>
@@ -3232,7 +3226,7 @@
         <v>1</v>
       </c>
       <c r="AD25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26" spans="1:30">
@@ -3297,10 +3291,10 @@
         <v>168</v>
       </c>
       <c r="U26" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V26" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="W26">
         <v>75</v>
@@ -3315,7 +3309,7 @@
         <v>1</v>
       </c>
       <c r="AD26" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="27" spans="1:30">
@@ -3380,10 +3374,10 @@
         <v>168</v>
       </c>
       <c r="U27" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V27" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="W27">
         <v>75</v>
@@ -3398,7 +3392,7 @@
         <v>1</v>
       </c>
       <c r="AD27" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28" spans="1:30">
@@ -3463,10 +3457,10 @@
         <v>168</v>
       </c>
       <c r="U28" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V28" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="W28">
         <v>75</v>
@@ -3481,7 +3475,7 @@
         <v>1</v>
       </c>
       <c r="AD28" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29" spans="1:30">
@@ -3546,10 +3540,10 @@
         <v>168</v>
       </c>
       <c r="U29" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V29" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="W29">
         <v>75</v>
@@ -3564,7 +3558,7 @@
         <v>1</v>
       </c>
       <c r="AD29" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30" spans="1:30">
@@ -3629,10 +3623,10 @@
         <v>168</v>
       </c>
       <c r="U30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="V30" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="W30">
         <v>75</v>
@@ -3647,7 +3641,7 @@
         <v>1</v>
       </c>
       <c r="AD30" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" spans="1:30">
@@ -3712,10 +3706,10 @@
         <v>163</v>
       </c>
       <c r="U31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="V31" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="W31">
         <v>75</v>
@@ -3730,7 +3724,7 @@
         <v>1</v>
       </c>
       <c r="AD31" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="32" spans="1:30">
@@ -3795,10 +3789,10 @@
         <v>166</v>
       </c>
       <c r="U32" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="V32" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="W32">
         <v>75</v>
@@ -3813,7 +3807,7 @@
         <v>1</v>
       </c>
       <c r="AD32" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="33" spans="1:30">
@@ -3878,10 +3872,10 @@
         <v>166</v>
       </c>
       <c r="U33" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="V33" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="W33">
         <v>75</v>
@@ -3896,7 +3890,7 @@
         <v>1</v>
       </c>
       <c r="AD33" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34" spans="1:30">
@@ -3961,10 +3955,10 @@
         <v>166</v>
       </c>
       <c r="U34" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="V34" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="W34">
         <v>75</v>
@@ -3979,7 +3973,7 @@
         <v>1</v>
       </c>
       <c r="AD34" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="35" spans="1:30">
@@ -4044,10 +4038,10 @@
         <v>164</v>
       </c>
       <c r="U35" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="V35" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="W35">
         <v>70</v>
@@ -4062,7 +4056,7 @@
         <v>1</v>
       </c>
       <c r="AD35" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -4083,61 +4077,61 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:21">
@@ -4148,10 +4142,10 @@
         <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E2">
         <v>-153903</v>
@@ -4196,10 +4190,10 @@
         <v>23</v>
       </c>
       <c r="S2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U2">
         <v>34</v>
@@ -4226,209 +4220,209 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
         <v>251</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="F3" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B8" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B9" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B10" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C10" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B11" t="s">
+        <v>247</v>
+      </c>
+      <c r="C11" t="s">
         <v>249</v>
       </c>
-      <c r="C11" t="s">
-        <v>251</v>
-      </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B12" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
